--- a/bases_historicas/base_consolidada_06-2026.xlsx
+++ b/bases_historicas/base_consolidada_06-2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ125"/>
+  <dimension ref="A1:AY126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -632,6 +632,46 @@
           <t>%_2026/2025</t>
         </is>
       </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>cod_uf</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>produto</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>milhoes_r$</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>uf_regioesnome_uf</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>uf_regioesregiao</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -767,6 +807,30 @@
       <c r="AQ2" t="n">
         <v>-0.1477492356937435</v>
       </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -902,6 +966,30 @@
       <c r="AQ3" t="n">
         <v>-0.144735375026774</v>
       </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1037,6 +1125,30 @@
       <c r="AQ4" t="n">
         <v>-0.3046397707586472</v>
       </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1172,6 +1284,30 @@
       <c r="AQ5" t="n">
         <v>0.04590561817211603</v>
       </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1307,6 +1443,30 @@
       <c r="AQ6" t="n">
         <v>-0.07958030437074204</v>
       </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1442,6 +1602,30 @@
       <c r="AQ7" t="n">
         <v>-0.3366112925492458</v>
       </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1593,6 +1777,30 @@
       <c r="AQ8" t="n">
         <v>0.01259420521597976</v>
       </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1744,6 +1952,30 @@
       <c r="AQ9" t="n">
         <v>0.09191339116488573</v>
       </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1923,6 +2155,30 @@
       <c r="AQ10" t="n">
         <v>-0.1942989061596975</v>
       </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2058,6 +2314,30 @@
       <c r="AQ11" t="n">
         <v>-0.1117422278449733</v>
       </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2217,6 +2497,30 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2352,6 +2656,30 @@
       <c r="AQ13" t="n">
         <v>0.08359147039035997</v>
       </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2513,6 +2841,30 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2648,6 +3000,30 @@
       <c r="AQ15" t="n">
         <v>-0.3614886570807894</v>
       </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2789,6 +3165,30 @@
       <c r="AQ16" t="n">
         <v>-1</v>
       </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2924,6 +3324,30 @@
       <c r="AQ17" t="n">
         <v>0.2687244626285463</v>
       </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3059,6 +3483,30 @@
       <c r="AQ18" t="n">
         <v>-0.07110976387488355</v>
       </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3218,6 +3666,30 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3353,6 +3825,30 @@
       <c r="AQ20" t="n">
         <v>0.03742051884185704</v>
       </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3488,6 +3984,30 @@
       <c r="AQ21" t="n">
         <v>-0.1530049413722474</v>
       </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3623,6 +4143,30 @@
       <c r="AQ22" t="n">
         <v>-0.1734924717057609</v>
       </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3758,6 +4302,30 @@
       <c r="AQ23" t="n">
         <v>-0.1692240276811933</v>
       </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3961,6 +4529,30 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4096,6 +4688,30 @@
       <c r="AQ25" t="n">
         <v>-0.03971758425956684</v>
       </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4253,6 +4869,30 @@
       <c r="AQ26" t="n">
         <v>0.03206216685625241</v>
       </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4410,6 +5050,30 @@
       <c r="AQ27" t="n">
         <v>-0.04436079664406711</v>
       </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4567,6 +5231,30 @@
       <c r="AQ28" t="n">
         <v>-0.0742773947458103</v>
       </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4724,6 +5412,30 @@
       <c r="AQ29" t="n">
         <v>-0.04045337327045928</v>
       </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4881,6 +5593,30 @@
       <c r="AQ30" t="n">
         <v>-0.2443135501141886</v>
       </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5038,6 +5774,30 @@
       <c r="AQ31" t="n">
         <v>-0.02954892692782762</v>
       </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5173,6 +5933,30 @@
       <c r="AQ32" t="n">
         <v>-0.0362153892529341</v>
       </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5308,6 +6092,30 @@
       <c r="AQ33" t="n">
         <v>-0.1623046230134449</v>
       </c>
+      <c r="AR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5443,6 +6251,30 @@
       <c r="AQ34" t="n">
         <v>-0.1308690726229079</v>
       </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5578,6 +6410,30 @@
       <c r="AQ35" t="n">
         <v>-0.3043837685703291</v>
       </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5713,6 +6569,30 @@
       <c r="AQ36" t="n">
         <v>0.02251180080502158</v>
       </c>
+      <c r="AR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5848,6 +6728,30 @@
       <c r="AQ37" t="n">
         <v>-0.1207206783576501</v>
       </c>
+      <c r="AR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5983,6 +6887,30 @@
       <c r="AQ38" t="n">
         <v>-0.4315494033687179</v>
       </c>
+      <c r="AR38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6134,6 +7062,30 @@
       <c r="AQ39" t="n">
         <v>-0.01612436888096913</v>
       </c>
+      <c r="AR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6285,6 +7237,30 @@
       <c r="AQ40" t="n">
         <v>0.07540445855671774</v>
       </c>
+      <c r="AR40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6464,6 +7440,30 @@
       <c r="AQ41" t="n">
         <v>-0.2548646391271715</v>
       </c>
+      <c r="AR41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6599,6 +7599,30 @@
       <c r="AQ42" t="n">
         <v>-0.08156137571914579</v>
       </c>
+      <c r="AR42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6758,6 +7782,30 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AR43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6893,6 +7941,30 @@
       <c r="AQ44" t="n">
         <v>0.1302470662615371</v>
       </c>
+      <c r="AR44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -7054,6 +8126,30 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AR45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -7189,6 +8285,30 @@
       <c r="AQ46" t="n">
         <v>-0.3761218357052035</v>
       </c>
+      <c r="AR46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -7330,6 +8450,30 @@
       <c r="AQ47" t="n">
         <v>-1</v>
       </c>
+      <c r="AR47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -7465,6 +8609,30 @@
       <c r="AQ48" t="n">
         <v>0.2108688733318391</v>
       </c>
+      <c r="AR48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -7600,6 +8768,30 @@
       <c r="AQ49" t="n">
         <v>-0.06849971080666761</v>
       </c>
+      <c r="AR49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -7759,6 +8951,30 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AR50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7894,6 +9110,30 @@
       <c r="AQ51" t="n">
         <v>0.01186367562223789</v>
       </c>
+      <c r="AR51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -8029,6 +9269,30 @@
       <c r="AQ52" t="n">
         <v>-0.1406601173444304</v>
       </c>
+      <c r="AR52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -8164,6 +9428,30 @@
       <c r="AQ53" t="n">
         <v>-0.1726922586413705</v>
       </c>
+      <c r="AR53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -8299,6 +9587,30 @@
       <c r="AQ54" t="n">
         <v>-0.1280095322180227</v>
       </c>
+      <c r="AR54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -8502,6 +9814,30 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AR55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -8637,6 +9973,30 @@
       <c r="AQ56" t="n">
         <v>-0.05078890261913405</v>
       </c>
+      <c r="AR56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -8794,6 +10154,30 @@
       <c r="AQ57" t="n">
         <v>0.05556533801765928</v>
       </c>
+      <c r="AR57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -8951,6 +10335,30 @@
       <c r="AQ58" t="n">
         <v>-0.1037870962900198</v>
       </c>
+      <c r="AR58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -9108,6 +10516,30 @@
       <c r="AQ59" t="n">
         <v>-0.08538514697789512</v>
       </c>
+      <c r="AR59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -9265,6 +10697,30 @@
       <c r="AQ60" t="n">
         <v>-0.05135885130628592</v>
       </c>
+      <c r="AR60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -9422,6 +10878,30 @@
       <c r="AQ61" t="n">
         <v>-0.1555238142007428</v>
       </c>
+      <c r="AR61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY61" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -9579,6 +11059,30 @@
       <c r="AQ62" t="n">
         <v>-0.02591193701644889</v>
       </c>
+      <c r="AR62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY62" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -9714,6 +11218,30 @@
       <c r="AQ63" t="n">
         <v>-0.04222100797271311</v>
       </c>
+      <c r="AR63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -9849,6 +11377,30 @@
       <c r="AQ64" t="n">
         <v>-0.1556386994536925</v>
       </c>
+      <c r="AR64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY64" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -9984,6 +11536,30 @@
       <c r="AQ65" t="n">
         <v>-0.1346345667197874</v>
       </c>
+      <c r="AR65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -10119,6 +11695,30 @@
       <c r="AQ66" t="n">
         <v>-0.3108405327089913</v>
       </c>
+      <c r="AR66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -10254,6 +11854,30 @@
       <c r="AQ67" t="n">
         <v>0.04512213111577457</v>
       </c>
+      <c r="AR67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY67" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -10389,6 +12013,30 @@
       <c r="AQ68" t="n">
         <v>-0.04832591019083032</v>
       </c>
+      <c r="AR68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY68" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -10524,6 +12172,30 @@
       <c r="AQ69" t="n">
         <v>-0.5203184280731676</v>
       </c>
+      <c r="AR69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY69" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -10675,6 +12347,30 @@
       <c r="AQ70" t="n">
         <v>-0.03134259812820295</v>
       </c>
+      <c r="AR70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY70" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -10826,6 +12522,30 @@
       <c r="AQ71" t="n">
         <v>0.05427561125353297</v>
       </c>
+      <c r="AR71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY71" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -11005,6 +12725,30 @@
       <c r="AQ72" t="n">
         <v>-0.2546658397561753</v>
       </c>
+      <c r="AR72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY72" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -11140,6 +12884,30 @@
       <c r="AQ73" t="n">
         <v>-0.07159360050667773</v>
       </c>
+      <c r="AR73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY73" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -11299,6 +13067,30 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AR74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -11434,6 +13226,30 @@
       <c r="AQ75" t="n">
         <v>0.1416159968591346</v>
       </c>
+      <c r="AR75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY75" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -11595,6 +13411,30 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AR76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY76" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -11730,6 +13570,30 @@
       <c r="AQ77" t="n">
         <v>-0.3664835448960276</v>
       </c>
+      <c r="AR77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY77" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -11869,6 +13733,30 @@
       <c r="AQ78" t="n">
         <v>-0.2056620933699921</v>
       </c>
+      <c r="AR78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY78" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -12004,6 +13892,30 @@
       <c r="AQ79" t="n">
         <v>0.1695079030725881</v>
       </c>
+      <c r="AR79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY79" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -12139,6 +14051,30 @@
       <c r="AQ80" t="n">
         <v>-0.04530497319769411</v>
       </c>
+      <c r="AR80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY80" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -12298,6 +14234,30 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AR81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY81" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -12433,6 +14393,30 @@
       <c r="AQ82" t="n">
         <v>0.00516554058134977</v>
       </c>
+      <c r="AR82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY82" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -12568,6 +14552,30 @@
       <c r="AQ83" t="n">
         <v>-0.08283159988181688</v>
       </c>
+      <c r="AR83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY83" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -12703,6 +14711,30 @@
       <c r="AQ84" t="n">
         <v>-0.1970892292043684</v>
       </c>
+      <c r="AR84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY84" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -12838,6 +14870,30 @@
       <c r="AQ85" t="n">
         <v>-0.08850027086830814</v>
       </c>
+      <c r="AR85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY85" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -13041,6 +15097,30 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AR86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY86" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -13176,6 +15256,30 @@
       <c r="AQ87" t="n">
         <v>-0.04825491394547021</v>
       </c>
+      <c r="AR87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY87" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -13333,6 +15437,30 @@
       <c r="AQ88" t="n">
         <v>0.0739688801663192</v>
       </c>
+      <c r="AR88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY88" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -13490,6 +15618,30 @@
       <c r="AQ89" t="n">
         <v>-0.1281021341327407</v>
       </c>
+      <c r="AR89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY89" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -13647,6 +15799,30 @@
       <c r="AQ90" t="n">
         <v>-0.09961898096106248</v>
       </c>
+      <c r="AR90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY90" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -13804,6 +15980,30 @@
       <c r="AQ91" t="n">
         <v>-0.05806958125620243</v>
       </c>
+      <c r="AR91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY91" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -13961,6 +16161,30 @@
       <c r="AQ92" t="n">
         <v>-0.09845933605775981</v>
       </c>
+      <c r="AR92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY92" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -14118,6 +16342,30 @@
       <c r="AQ93" t="n">
         <v>-0.02103966684572445</v>
       </c>
+      <c r="AR93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY93" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -14253,6 +16501,30 @@
       <c r="AQ94" t="n">
         <v>-0.03870955817030419</v>
       </c>
+      <c r="AR94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY94" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -14388,6 +16660,30 @@
       <c r="AQ95" t="n">
         <v>-0.1168929827771792</v>
       </c>
+      <c r="AR95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY95" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -14523,6 +16819,30 @@
       <c r="AQ96" t="n">
         <v>-0.1352829990226698</v>
       </c>
+      <c r="AR96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY96" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -14658,6 +16978,30 @@
       <c r="AQ97" t="n">
         <v>-0.3044354858732528</v>
       </c>
+      <c r="AR97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY97" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -14793,6 +17137,30 @@
       <c r="AQ98" t="n">
         <v>0.03974687842150981</v>
       </c>
+      <c r="AR98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY98" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -14928,6 +17296,30 @@
       <c r="AQ99" t="n">
         <v>0.006952748022160948</v>
       </c>
+      <c r="AR99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY99" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -15063,6 +17455,30 @@
       <c r="AQ100" t="n">
         <v>-0.5470944717349852</v>
       </c>
+      <c r="AR100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY100" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -15214,6 +17630,30 @@
       <c r="AQ101" t="n">
         <v>-0.05528612197641947</v>
       </c>
+      <c r="AR101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY101" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -15365,6 +17805,30 @@
       <c r="AQ102" t="n">
         <v>0.02189291393770132</v>
       </c>
+      <c r="AR102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY102" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -15544,6 +18008,30 @@
       <c r="AQ103" t="n">
         <v>-0.2565969483826996</v>
       </c>
+      <c r="AR103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY103" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -15679,6 +18167,30 @@
       <c r="AQ104" t="n">
         <v>-0.07531577390127897</v>
       </c>
+      <c r="AR104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY104" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -15838,6 +18350,30 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AR105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY105" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -15973,6 +18509,30 @@
       <c r="AQ106" t="n">
         <v>0.1174433643050921</v>
       </c>
+      <c r="AR106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY106" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -16134,6 +18694,30 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AR107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY107" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -16269,6 +18853,30 @@
       <c r="AQ108" t="n">
         <v>-0.3653811701925</v>
       </c>
+      <c r="AR108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY108" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -16408,6 +19016,30 @@
       <c r="AQ109" t="n">
         <v>-0.2038406459359604</v>
       </c>
+      <c r="AR109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY109" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -16543,6 +19175,30 @@
       <c r="AQ110" t="n">
         <v>0.1247402087805252</v>
       </c>
+      <c r="AR110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY110" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -16678,6 +19334,30 @@
       <c r="AQ111" t="n">
         <v>-0.05435766796337427</v>
       </c>
+      <c r="AR111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY111" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -16837,6 +19517,30 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AR112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY112" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -16972,6 +19676,30 @@
       <c r="AQ113" t="n">
         <v>-0.004969953223310508</v>
       </c>
+      <c r="AR113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY113" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -17107,6 +19835,30 @@
       <c r="AQ114" t="n">
         <v>-0.01979222948205006</v>
       </c>
+      <c r="AR114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY114" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -17242,6 +19994,30 @@
       <c r="AQ115" t="n">
         <v>-0.1894961932674049</v>
       </c>
+      <c r="AR115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY115" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -17377,6 +20153,30 @@
       <c r="AQ116" t="n">
         <v>-0.09165895556976034</v>
       </c>
+      <c r="AR116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY116" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -17580,6 +20380,30 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AR117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -17715,6 +20539,30 @@
       <c r="AQ118" t="n">
         <v>-0.05496713936387976</v>
       </c>
+      <c r="AR118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -17872,6 +20720,30 @@
       <c r="AQ119" t="n">
         <v>0.08818536138406108</v>
       </c>
+      <c r="AR119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -18029,6 +20901,30 @@
       <c r="AQ120" t="n">
         <v>-0.1667073764313325</v>
       </c>
+      <c r="AR120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -18186,6 +21082,30 @@
       <c r="AQ121" t="n">
         <v>-0.1043542569700028</v>
       </c>
+      <c r="AR121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -18343,6 +21263,30 @@
       <c r="AQ122" t="n">
         <v>-0.05472336231550468</v>
       </c>
+      <c r="AR122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -18500,6 +21444,30 @@
       <c r="AQ123" t="n">
         <v>-0.07951467522900968</v>
       </c>
+      <c r="AR123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -18657,6 +21625,30 @@
       <c r="AQ124" t="n">
         <v>-0.01920298720380165</v>
       </c>
+      <c r="AR124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -18791,6 +21783,197 @@
       </c>
       <c r="AQ125" t="n">
         <v>-0.04242337832015575</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026 - 04</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>ALGODÃO</t>
+        </is>
+      </c>
+      <c r="AT126" t="n">
+        <v>2018</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>91430521.9375</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>91.43049999999999</v>
+      </c>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>LAVOURAS</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>RONDÔNIA</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/bases_historicas/base_consolidada_06-2026.xlsx
+++ b/bases_historicas/base_consolidada_06-2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY126"/>
+  <dimension ref="A1:AY157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21812,165 +21812,5448 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026 - 04</t>
-        </is>
-      </c>
-      <c r="B126" t="n">
-        <v>0</v>
+          <t>2026 - 05</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Algodão</t>
+        </is>
       </c>
       <c r="C126" t="n">
-        <v>0</v>
+        <v>10.47807424342295</v>
       </c>
       <c r="D126" t="n">
-        <v>0</v>
+        <v>8.699733011499795</v>
       </c>
       <c r="E126" t="n">
-        <v>0</v>
+        <v>9.791833441009336</v>
       </c>
       <c r="F126" t="n">
-        <v>0</v>
+        <v>8.543812258634945</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>5.175751861299879</v>
       </c>
       <c r="H126" t="n">
-        <v>0</v>
+        <v>6.674175696827548</v>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
+        <v>6.269406592502849</v>
       </c>
       <c r="J126" t="n">
-        <v>0</v>
+        <v>4.316177404254262</v>
       </c>
       <c r="K126" t="n">
-        <v>0</v>
+        <v>4.027461433576061</v>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>4.8853709674333</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>6.318220782625176</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>8.355736257986072</v>
       </c>
       <c r="O126" t="n">
-        <v>0</v>
+        <v>9.528229556310167</v>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>7.924109539668575</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>10.35397471959551</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>18.44931762440651</v>
       </c>
       <c r="S126" t="n">
-        <v>0</v>
+        <v>13.32011649956185</v>
       </c>
       <c r="T126" t="n">
-        <v>0</v>
+        <v>9.81334616726615</v>
       </c>
       <c r="U126" t="n">
-        <v>0</v>
+        <v>13.58457933436449</v>
       </c>
       <c r="V126" t="n">
-        <v>0</v>
+        <v>12.74471675829004</v>
       </c>
       <c r="W126" t="n">
-        <v>0</v>
+        <v>8.786027710591092</v>
       </c>
       <c r="X126" t="n">
-        <v>0</v>
+        <v>8.500304010823037</v>
       </c>
       <c r="Y126" t="n">
-        <v>0</v>
+        <v>22.21350056001249</v>
       </c>
       <c r="Z126" t="n">
-        <v>0</v>
+        <v>27.66940712664022</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>19.67861622441871</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>25.3006555165732</v>
       </c>
       <c r="AC126" t="n">
-        <v>0</v>
+        <v>25.88845698940602</v>
       </c>
       <c r="AD126" t="n">
-        <v>0</v>
+        <v>23.50398343954763</v>
       </c>
       <c r="AE126" t="n">
-        <v>0</v>
+        <v>16.1313858044427</v>
       </c>
       <c r="AF126" t="n">
-        <v>0</v>
+        <v>24.02460566963629</v>
       </c>
       <c r="AG126" t="n">
-        <v>0</v>
+        <v>27.63102470616465</v>
       </c>
       <c r="AH126" t="n">
-        <v>0</v>
+        <v>29.83880752174289</v>
       </c>
       <c r="AI126" t="n">
-        <v>0</v>
+        <v>30.73652247581139</v>
       </c>
       <c r="AJ126" t="n">
-        <v>0</v>
+        <v>36.67556885075948</v>
       </c>
       <c r="AK126" t="n">
-        <v>0</v>
+        <v>33.31130990082782</v>
       </c>
       <c r="AL126" t="n">
-        <v>0</v>
+        <v>35.23714747097601</v>
       </c>
       <c r="AM126" t="n">
-        <v>0</v>
+        <v>36.93869443802068</v>
       </c>
       <c r="AN126" t="n">
-        <v>0</v>
+        <v>33.18491635036324</v>
       </c>
       <c r="AO126" t="n">
-        <v>0</v>
+        <v>0.05781332453997368</v>
       </c>
       <c r="AP126" t="n">
-        <v>0</v>
+        <v>0.04828844242985886</v>
       </c>
       <c r="AQ126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR126" t="inlineStr">
+        <v>-0.1016218397744375</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026 - 05</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Amendoim</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>0.8008369901095054</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.6444178515733443</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.7204900999817291</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.5828624539389156</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.7157108119013494</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.6688837631247113</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.598074239577041</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.5717396422568807</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.6005474452593654</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.6451723778201249</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.7908593695996162</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.8794653863813301</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.6305961730250408</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.7993730471315134</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.9316447295992352</v>
+      </c>
+      <c r="R127" t="n">
+        <v>1.074350484682292</v>
+      </c>
+      <c r="S127" t="n">
+        <v>1.128006468722172</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.8550757132979787</v>
+      </c>
+      <c r="U127" t="n">
+        <v>1.078411285123155</v>
+      </c>
+      <c r="V127" t="n">
+        <v>1.538658532736727</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.9443442267463491</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.9097208739036758</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>1.247460564459252</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>1.398204974812198</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>1.721934889666778</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>1.944379501649503</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>2.080514475065387</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>2.33704334643636</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>2.410712939748096</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>2.178804295266814</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>2.534655025380678</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>3.49822546844165</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>3.203016618285674</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>3.76667582844837</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>4.79673106100732</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>4.524659275570605</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>6.439655016133499</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>5.485825638414935</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05672025009873694</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.4232353474442323</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>-0.1481180863460699</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026 - 05</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Arroz</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>24.16722004943198</v>
+      </c>
+      <c r="D128" t="n">
+        <v>19.67781239902399</v>
+      </c>
+      <c r="E128" t="n">
+        <v>28.80860150052676</v>
+      </c>
+      <c r="F128" t="n">
+        <v>24.32167257901606</v>
+      </c>
+      <c r="G128" t="n">
+        <v>24.51651191938845</v>
+      </c>
+      <c r="H128" t="n">
+        <v>23.34732251984698</v>
+      </c>
+      <c r="I128" t="n">
+        <v>20.45581626649677</v>
+      </c>
+      <c r="J128" t="n">
+        <v>16.60135159613149</v>
+      </c>
+      <c r="K128" t="n">
+        <v>16.52612178025817</v>
+      </c>
+      <c r="L128" t="n">
+        <v>18.37143485353934</v>
+      </c>
+      <c r="M128" t="n">
+        <v>24.8272171527053</v>
+      </c>
+      <c r="N128" t="n">
+        <v>18.1412522197366</v>
+      </c>
+      <c r="O128" t="n">
+        <v>17.7503564725585</v>
+      </c>
+      <c r="P128" t="n">
+        <v>21.26613212486099</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>25.70010361725803</v>
+      </c>
+      <c r="R128" t="n">
+        <v>32.7162921984533</v>
+      </c>
+      <c r="S128" t="n">
+        <v>23.86577342495722</v>
+      </c>
+      <c r="T128" t="n">
+        <v>18.87068709025893</v>
+      </c>
+      <c r="U128" t="n">
+        <v>18.93959699148735</v>
+      </c>
+      <c r="V128" t="n">
+        <v>24.33327210606822</v>
+      </c>
+      <c r="W128" t="n">
+        <v>26.00004055701707</v>
+      </c>
+      <c r="X128" t="n">
+        <v>20.15211662074561</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>19.77873511665907</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>17.79550874084158</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>21.5935347915071</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>22.15245527792219</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>20.61505099085333</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>18.87267185132882</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>20.60058001935034</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>17.16509927136913</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>16.21418411542675</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>22.35982960932603</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>22.38384988931005</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>17.95733289430454</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>22.25235830017252</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>25.79861313505929</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>21.56417115433081</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>15.08443518494829</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.1593653484745159</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>-0.1641344811273614</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>-0.3004862057070609</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026 - 05</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>15.95195420200865</v>
+      </c>
+      <c r="D129" t="n">
+        <v>17.55067445481692</v>
+      </c>
+      <c r="E129" t="n">
+        <v>15.12671955398412</v>
+      </c>
+      <c r="F129" t="n">
+        <v>12.18326902578111</v>
+      </c>
+      <c r="G129" t="n">
+        <v>12.1459623010039</v>
+      </c>
+      <c r="H129" t="n">
+        <v>17.7722978260339</v>
+      </c>
+      <c r="I129" t="n">
+        <v>23.6101422672552</v>
+      </c>
+      <c r="J129" t="n">
+        <v>16.17504642801935</v>
+      </c>
+      <c r="K129" t="n">
+        <v>14.06276942129088</v>
+      </c>
+      <c r="L129" t="n">
+        <v>14.17088574599683</v>
+      </c>
+      <c r="M129" t="n">
+        <v>15.04686980440638</v>
+      </c>
+      <c r="N129" t="n">
+        <v>13.08350325506925</v>
+      </c>
+      <c r="O129" t="n">
+        <v>12.78115613263752</v>
+      </c>
+      <c r="P129" t="n">
+        <v>12.49039971435246</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>13.00373698201922</v>
+      </c>
+      <c r="R129" t="n">
+        <v>12.86522958721086</v>
+      </c>
+      <c r="S129" t="n">
+        <v>13.0932257305916</v>
+      </c>
+      <c r="T129" t="n">
+        <v>13.56968665732466</v>
+      </c>
+      <c r="U129" t="n">
+        <v>14.35025218381215</v>
+      </c>
+      <c r="V129" t="n">
+        <v>14.46185837206388</v>
+      </c>
+      <c r="W129" t="n">
+        <v>13.917134632716</v>
+      </c>
+      <c r="X129" t="n">
+        <v>15.56877228545592</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>16.96841500534499</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>15.99273866638928</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>18.2014308267025</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>19.23392290925356</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>18.84156908082856</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>27.74469465768298</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>20.3437285280892</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>17.62223450061854</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>20.29719177963434</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>15.70323448410513</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>13.99191930998539</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>16.72479191104483</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>19.21795990142286</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>22.94347459228712</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>22.07360789517725</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>22.72555277254131</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.1938558884488268</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>-0.03791346832019493</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.02953503933113266</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026 - 05</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Batata - inglesa</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>7.93634875304654</v>
+      </c>
+      <c r="D130" t="n">
+        <v>9.910369736138449</v>
+      </c>
+      <c r="E130" t="n">
+        <v>7.28363372232826</v>
+      </c>
+      <c r="F130" t="n">
+        <v>7.77278675958599</v>
+      </c>
+      <c r="G130" t="n">
+        <v>5.904893676440363</v>
+      </c>
+      <c r="H130" t="n">
+        <v>11.60268422596555</v>
+      </c>
+      <c r="I130" t="n">
+        <v>8.793258503770973</v>
+      </c>
+      <c r="J130" t="n">
+        <v>6.047549126168968</v>
+      </c>
+      <c r="K130" t="n">
+        <v>7.313808886241138</v>
+      </c>
+      <c r="L130" t="n">
+        <v>9.376569668954119</v>
+      </c>
+      <c r="M130" t="n">
+        <v>6.519339875270946</v>
+      </c>
+      <c r="N130" t="n">
+        <v>6.477634909883884</v>
+      </c>
+      <c r="O130" t="n">
+        <v>9.522171297464327</v>
+      </c>
+      <c r="P130" t="n">
+        <v>8.30960721266279</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>7.867794578780631</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6.423096951727898</v>
+      </c>
+      <c r="S130" t="n">
+        <v>7.498929944105898</v>
+      </c>
+      <c r="T130" t="n">
+        <v>7.053275119869452</v>
+      </c>
+      <c r="U130" t="n">
+        <v>7.612228463090785</v>
+      </c>
+      <c r="V130" t="n">
+        <v>7.729838237831534</v>
+      </c>
+      <c r="W130" t="n">
+        <v>9.5813838652369</v>
+      </c>
+      <c r="X130" t="n">
+        <v>10.19709137532212</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>8.416187089198926</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>6.63435845669903</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>9.919103591485172</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>11.54584241269886</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>11.40856341765772</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>13.74654890250528</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>7.377396753556061</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>7.046983914208648</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>13.18671489157149</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>10.58632841380675</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>9.765879066452555</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>11.94010242198589</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>12.84672667741348</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>20.15340172688432</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>9.337031840467143</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>11.42144551356727</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.5687577258351031</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>-0.5367019440687428</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.2232415727732857</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026 - 05</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Cacau</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>4.866760813875181</v>
+      </c>
+      <c r="D131" t="n">
+        <v>3.844686501796087</v>
+      </c>
+      <c r="E131" t="n">
+        <v>4.14161491251749</v>
+      </c>
+      <c r="F131" t="n">
+        <v>3.817965147411107</v>
+      </c>
+      <c r="G131" t="n">
+        <v>4.052958422031626</v>
+      </c>
+      <c r="H131" t="n">
+        <v>3.621828136635934</v>
+      </c>
+      <c r="I131" t="n">
+        <v>3.071829645219127</v>
+      </c>
+      <c r="J131" t="n">
+        <v>2.553204665865638</v>
+      </c>
+      <c r="K131" t="n">
+        <v>3.438775562385694</v>
+      </c>
+      <c r="L131" t="n">
+        <v>3.716453144781136</v>
+      </c>
+      <c r="M131" t="n">
+        <v>2.720606013541624</v>
+      </c>
+      <c r="N131" t="n">
+        <v>1.950818634086818</v>
+      </c>
+      <c r="O131" t="n">
+        <v>2.534197604942841</v>
+      </c>
+      <c r="P131" t="n">
+        <v>4.791595323071719</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>3.985524581211543</v>
+      </c>
+      <c r="R131" t="n">
+        <v>3.268199852245736</v>
+      </c>
+      <c r="S131" t="n">
+        <v>2.748287419114068</v>
+      </c>
+      <c r="T131" t="n">
+        <v>2.435826484088029</v>
+      </c>
+      <c r="U131" t="n">
+        <v>2.591940378765655</v>
+      </c>
+      <c r="V131" t="n">
+        <v>2.934287787317558</v>
+      </c>
+      <c r="W131" t="n">
+        <v>3.774415009420772</v>
+      </c>
+      <c r="X131" t="n">
+        <v>3.803655295078411</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>3.247866863360561</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>2.997883292438371</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>2.867342605341551</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>2.338723922538754</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>2.71391625703517</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>3.538655951295276</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>2.575972510030073</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>3.492053327199998</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>3.667571520570299</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>4.606473297393821</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>4.71563292308956</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>3.484234158174662</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>4.503812755918196</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>11.45649863949095</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>11.99627654744613</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>5.18185908475757</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>1.543733334481243</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.04711543421255704</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>-0.5680443790818805</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026 - 05</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Café</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" t="n">
+        <v>37.48127630625545</v>
+      </c>
+      <c r="L132" t="n">
+        <v>38.24839024944563</v>
+      </c>
+      <c r="M132" t="n">
+        <v>37.08350445159244</v>
+      </c>
+      <c r="N132" t="n">
+        <v>34.07345770202734</v>
+      </c>
+      <c r="O132" t="n">
+        <v>21.19647464121097</v>
+      </c>
+      <c r="P132" t="n">
+        <v>29.49473011605953</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>24.47315234527053</v>
+      </c>
+      <c r="R132" t="n">
+        <v>34.69425715809414</v>
+      </c>
+      <c r="S132" t="n">
+        <v>36.77117980335158</v>
+      </c>
+      <c r="T132" t="n">
+        <v>38.70081780755057</v>
+      </c>
+      <c r="U132" t="n">
+        <v>32.45776062513808</v>
+      </c>
+      <c r="V132" t="n">
+        <v>37.43054588022393</v>
+      </c>
+      <c r="W132" t="n">
+        <v>32.42962756473897</v>
+      </c>
+      <c r="X132" t="n">
+        <v>43.23149425271936</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>49.99625236846886</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>45.82803795184164</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>32.37270311607443</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>38.77772873486497</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>38.63751860053636</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>46.10413575914516</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>39.33402899643028</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>43.30848652035578</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>32.14762401527563</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>45.9572663466315</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>47.42473021274113</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>59.24666880255934</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>54.12419551493663</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>81.64057608158349</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>118.9769297815107</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>109.5945621818942</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.5083933406280963</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.4573259461400294</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>-0.07885871333918537</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026 - 05</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Café arábica</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" t="n">
+        <v>37.48127630625545</v>
+      </c>
+      <c r="L133" t="n">
+        <v>38.24839024944563</v>
+      </c>
+      <c r="M133" t="n">
+        <v>37.08350445159244</v>
+      </c>
+      <c r="N133" t="n">
+        <v>34.07345770202734</v>
+      </c>
+      <c r="O133" t="n">
+        <v>21.19647464121097</v>
+      </c>
+      <c r="P133" t="n">
+        <v>29.49473011605953</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>24.47315234527053</v>
+      </c>
+      <c r="R133" t="n">
+        <v>34.69425715809414</v>
+      </c>
+      <c r="S133" t="n">
+        <v>36.77117980335158</v>
+      </c>
+      <c r="T133" t="n">
+        <v>38.70081780755057</v>
+      </c>
+      <c r="U133" t="n">
+        <v>32.45776062513808</v>
+      </c>
+      <c r="V133" t="n">
+        <v>37.43054588022393</v>
+      </c>
+      <c r="W133" t="n">
+        <v>32.42962756473897</v>
+      </c>
+      <c r="X133" t="n">
+        <v>43.23149425271936</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>42.87317720647071</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>37.34877527441261</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>26.27537291659778</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>31.33994992499883</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>31.33083763587262</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>39.80464782469708</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>30.52625919303798</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>34.69453934462715</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>24.58103336503169</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>38.29734391938747</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>35.78988608851844</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>45.07246649075284</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>41.24305478185363</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>59.1210060909025</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>86.00436604059217</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>85.6641740396426</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.4334778644213066</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.4547175653329496</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>-0.003955520127769008</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026 - 05</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Café conilon</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y134" t="n">
+        <v>7.123075161998144</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>8.479262677429023</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>6.097330199476644</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>7.437778809866147</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>7.306680964663745</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>6.299487934448086</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>8.807769803392295</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>8.613947175728629</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>7.566590650243946</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>7.659922427244024</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>11.63484412422269</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>14.1742023118065</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>12.881140733083</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>22.51956999068099</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>32.97256374091853</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>23.93038814225156</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.7482589824396011</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.4641737721707468</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>-0.274233319244319</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026 - 05</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Cana-de-açúcar</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>35.81836570539804</v>
+      </c>
+      <c r="D135" t="n">
+        <v>38.33374769882376</v>
+      </c>
+      <c r="E135" t="n">
+        <v>38.38628860353398</v>
+      </c>
+      <c r="F135" t="n">
+        <v>41.1111930028433</v>
+      </c>
+      <c r="G135" t="n">
+        <v>34.78312016896502</v>
+      </c>
+      <c r="H135" t="n">
+        <v>41.13996788376677</v>
+      </c>
+      <c r="I135" t="n">
+        <v>39.1629701279065</v>
+      </c>
+      <c r="J135" t="n">
+        <v>44.64644525098744</v>
+      </c>
+      <c r="K135" t="n">
+        <v>47.63314811926122</v>
+      </c>
+      <c r="L135" t="n">
+        <v>48.37565446937481</v>
+      </c>
+      <c r="M135" t="n">
+        <v>37.39097682710626</v>
+      </c>
+      <c r="N135" t="n">
+        <v>39.82556416604538</v>
+      </c>
+      <c r="O135" t="n">
+        <v>51.49125319783188</v>
+      </c>
+      <c r="P135" t="n">
+        <v>49.74387202109777</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>50.61357049098038</v>
+      </c>
+      <c r="R135" t="n">
+        <v>45.91006689010688</v>
+      </c>
+      <c r="S135" t="n">
+        <v>49.14505553521374</v>
+      </c>
+      <c r="T135" t="n">
+        <v>67.48005714739088</v>
+      </c>
+      <c r="U135" t="n">
+        <v>69.87930339472346</v>
+      </c>
+      <c r="V135" t="n">
+        <v>63.22034582793076</v>
+      </c>
+      <c r="W135" t="n">
+        <v>77.35218550135679</v>
+      </c>
+      <c r="X135" t="n">
+        <v>86.80377979625459</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>104.3983176382372</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>111.914302562488</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>116.4094711488999</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>104.5251397764861</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>98.94328394573193</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>103.9458180400389</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>127.2110669288955</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>105.9393682154473</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>95.70990490973881</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>92.74046062463127</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>97.37641434331877</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>105.2238097624351</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>124.6393765996448</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>124.5852702304026</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>121.1917407528647</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>110.7643069653787</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>-0.0004341033365085067</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>-0.0272386091169694</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>-0.08604079554191446</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026 - 05</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Cebola</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>3.301342630239734</v>
+      </c>
+      <c r="D136" t="n">
+        <v>5.675437716446144</v>
+      </c>
+      <c r="E136" t="n">
+        <v>2.751245523422965</v>
+      </c>
+      <c r="F136" t="n">
+        <v>4.851607611867056</v>
+      </c>
+      <c r="G136" t="n">
+        <v>2.507417082184786</v>
+      </c>
+      <c r="H136" t="n">
+        <v>3.5646433423266</v>
+      </c>
+      <c r="I136" t="n">
+        <v>4.227961397063913</v>
+      </c>
+      <c r="J136" t="n">
+        <v>1.865850062417102</v>
+      </c>
+      <c r="K136" t="n">
+        <v>3.670345038137197</v>
+      </c>
+      <c r="L136" t="n">
+        <v>3.03125324362192</v>
+      </c>
+      <c r="M136" t="n">
+        <v>3.027815615609419</v>
+      </c>
+      <c r="N136" t="n">
+        <v>3.081153426231495</v>
+      </c>
+      <c r="O136" t="n">
+        <v>3.11687037042912</v>
+      </c>
+      <c r="P136" t="n">
+        <v>3.317363621071113</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>2.958183958453264</v>
+      </c>
+      <c r="R136" t="n">
+        <v>3.395874750109971</v>
+      </c>
+      <c r="S136" t="n">
+        <v>2.485664135355018</v>
+      </c>
+      <c r="T136" t="n">
+        <v>2.36514111963813</v>
+      </c>
+      <c r="U136" t="n">
+        <v>2.53537557001502</v>
+      </c>
+      <c r="V136" t="n">
+        <v>4.008721834425029</v>
+      </c>
+      <c r="W136" t="n">
+        <v>3.641478601214265</v>
+      </c>
+      <c r="X136" t="n">
+        <v>5.987360114671409</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>2.359807509318819</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>3.06778075236032</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>6.798489256381126</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>7.951322093915469</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>6.016080160951333</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>6.857448362008326</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>3.467203285373209</v>
+      </c>
+      <c r="AF136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AK136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AN136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AP136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AQ136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AR136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026 - 05</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Feijão</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>20.75297067482841</v>
+      </c>
+      <c r="D137" t="n">
+        <v>17.27146018889498</v>
+      </c>
+      <c r="E137" t="n">
+        <v>18.7708475928769</v>
+      </c>
+      <c r="F137" t="n">
+        <v>18.0560075053759</v>
+      </c>
+      <c r="G137" t="n">
+        <v>18.85605320896483</v>
+      </c>
+      <c r="H137" t="n">
+        <v>25.68699048388262</v>
+      </c>
+      <c r="I137" t="n">
+        <v>15.14300729439573</v>
+      </c>
+      <c r="J137" t="n">
+        <v>13.86765443371828</v>
+      </c>
+      <c r="K137" t="n">
+        <v>14.39672512944839</v>
+      </c>
+      <c r="L137" t="n">
+        <v>18.93231536308587</v>
+      </c>
+      <c r="M137" t="n">
+        <v>15.86542281932221</v>
+      </c>
+      <c r="N137" t="n">
+        <v>12.3238969786196</v>
+      </c>
+      <c r="O137" t="n">
+        <v>13.8353547045237</v>
+      </c>
+      <c r="P137" t="n">
+        <v>18.36806931262625</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>18.9964328111951</v>
+      </c>
+      <c r="R137" t="n">
+        <v>13.29639369414136</v>
+      </c>
+      <c r="S137" t="n">
+        <v>14.4593701787265</v>
+      </c>
+      <c r="T137" t="n">
+        <v>14.84266382927449</v>
+      </c>
+      <c r="U137" t="n">
+        <v>14.19710221247719</v>
+      </c>
+      <c r="V137" t="n">
+        <v>25.4492269662198</v>
+      </c>
+      <c r="W137" t="n">
+        <v>17.28074850954529</v>
+      </c>
+      <c r="X137" t="n">
+        <v>15.59929015394092</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>15.32197577538899</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>18.03829681802248</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>18.90282451487155</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>17.13070479649601</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>16.36337980676306</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>21.14345595500261</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>15.49655088609827</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>10.02475747888459</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>15.7146110047653</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>17.40103409954092</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>14.80238605595523</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>16.30049617770777</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>16.38525687138634</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>15.33301901753084</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>12.18669090411282</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>13.72155089555721</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.06421857540073272</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>-0.2051995181001668</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.1259455912618901</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026 - 05</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Fumo</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>7.084293798640888</v>
+      </c>
+      <c r="D138" t="n">
+        <v>7.360632501671528</v>
+      </c>
+      <c r="E138" t="n">
+        <v>6.730499315107848</v>
+      </c>
+      <c r="F138" t="n">
+        <v>13.64797264471515</v>
+      </c>
+      <c r="G138" t="n">
+        <v>13.75321979806218</v>
+      </c>
+      <c r="H138" t="n">
+        <v>9.391263229892841</v>
+      </c>
+      <c r="I138" t="n">
+        <v>7.728796259891666</v>
+      </c>
+      <c r="J138" t="n">
+        <v>8.983069081085134</v>
+      </c>
+      <c r="K138" t="n">
+        <v>10.09187850161482</v>
+      </c>
+      <c r="L138" t="n">
+        <v>8.509643611379737</v>
+      </c>
+      <c r="M138" t="n">
+        <v>9.948078595664221</v>
+      </c>
+      <c r="N138" t="n">
+        <v>8.349156692838521</v>
+      </c>
+      <c r="O138" t="n">
+        <v>8.058859330822028</v>
+      </c>
+      <c r="P138" t="n">
+        <v>9.377440255271171</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>10.13506829405984</v>
+      </c>
+      <c r="R138" t="n">
+        <v>14.90965420204461</v>
+      </c>
+      <c r="S138" t="n">
+        <v>14.64646298180664</v>
+      </c>
+      <c r="T138" t="n">
+        <v>14.94326128742589</v>
+      </c>
+      <c r="U138" t="n">
+        <v>15.49980439615818</v>
+      </c>
+      <c r="V138" t="n">
+        <v>15.24702232326761</v>
+      </c>
+      <c r="W138" t="n">
+        <v>15.36241483049352</v>
+      </c>
+      <c r="X138" t="n">
+        <v>12.62635473330297</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>12.52100564820013</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>13.38855589912193</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>15.21154052969435</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>15.5253015721375</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>15.0110919495148</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>10.65616521033115</v>
+      </c>
+      <c r="AE138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AJ138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AK138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AN138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AP138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AQ138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AR138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026 - 05</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Laranja</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>26.14127306881626</v>
+      </c>
+      <c r="D139" t="n">
+        <v>26.87919094101456</v>
+      </c>
+      <c r="E139" t="n">
+        <v>24.6952232574047</v>
+      </c>
+      <c r="F139" t="n">
+        <v>23.45505036822333</v>
+      </c>
+      <c r="G139" t="n">
+        <v>20.01794171685568</v>
+      </c>
+      <c r="H139" t="n">
+        <v>23.90585155278064</v>
+      </c>
+      <c r="I139" t="n">
+        <v>26.12970646803845</v>
+      </c>
+      <c r="J139" t="n">
+        <v>17.95547905257439</v>
+      </c>
+      <c r="K139" t="n">
+        <v>22.19918976156006</v>
+      </c>
+      <c r="L139" t="n">
+        <v>24.23178089840518</v>
+      </c>
+      <c r="M139" t="n">
+        <v>23.92889149448836</v>
+      </c>
+      <c r="N139" t="n">
+        <v>15.1970650715926</v>
+      </c>
+      <c r="O139" t="n">
+        <v>27.26352572377343</v>
+      </c>
+      <c r="P139" t="n">
+        <v>32.97402350266084</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>27.5563956494866</v>
+      </c>
+      <c r="R139" t="n">
+        <v>24.62067601170911</v>
+      </c>
+      <c r="S139" t="n">
+        <v>23.51332276588374</v>
+      </c>
+      <c r="T139" t="n">
+        <v>28.03841546535526</v>
+      </c>
+      <c r="U139" t="n">
+        <v>26.42307626869751</v>
+      </c>
+      <c r="V139" t="n">
+        <v>27.19500328744664</v>
+      </c>
+      <c r="W139" t="n">
+        <v>23.82584757201766</v>
+      </c>
+      <c r="X139" t="n">
+        <v>30.92658513827417</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>34.37598446028237</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>20.40259533840609</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>22.06077563218452</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>26.61078643997348</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>22.50348358148561</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>23.99838200726146</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>26.67399465483814</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>21.63729100700781</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>21.6462594884511</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>19.63557268485754</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>19.20748307782694</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>18.46100548617127</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>22.63595014619412</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>29.30445200068603</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>25.26074926255386</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>15.66743931680361</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.2945978327140431</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>-0.1379893655079271</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>-0.3797713933992934</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026 - 05</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Mamona</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>0.4950936912110389</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.3366873300520679</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.250742260522281</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.2137900056584086</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.1084869215201305</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.1267178943163407</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.08006269245244169</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.09756456928252664</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.204000490836848</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.0325827159806841</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.0789962978260062</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.3316348232777049</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.2245433972651381</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.1695123145373077</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.2291477036231183</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.426346555207095</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.4111030163141514</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.1886304717315539</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.2048035368625337</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.2712079731703524</v>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.3620631135350083</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.08318823436707959</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.04025681196352992</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.1160584513238606</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.1287836237215675</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.08461126643225599</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.05131924141176136</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.08374678716620518</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.1080569466751818</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.1320745729544723</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.1017299857518935</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.1319848617435219</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.11283363726356</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.1275519143078972</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.1568632378715308</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.125372585943682</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.1304422812317734</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.229799166266365</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>-0.200752275390613</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026 - 05</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Mandioca</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>15.32759904080017</v>
+      </c>
+      <c r="D141" t="n">
+        <v>13.29265285790154</v>
+      </c>
+      <c r="E141" t="n">
+        <v>14.60785703180297</v>
+      </c>
+      <c r="F141" t="n">
+        <v>15.18794227178065</v>
+      </c>
+      <c r="G141" t="n">
+        <v>13.32082945712863</v>
+      </c>
+      <c r="H141" t="n">
+        <v>11.35428637483584</v>
+      </c>
+      <c r="I141" t="n">
+        <v>17.26436482451615</v>
+      </c>
+      <c r="J141" t="n">
+        <v>12.62252080332999</v>
+      </c>
+      <c r="K141" t="n">
+        <v>13.16706500336975</v>
+      </c>
+      <c r="L141" t="n">
+        <v>11.98077776664585</v>
+      </c>
+      <c r="M141" t="n">
+        <v>12.63565659485028</v>
+      </c>
+      <c r="N141" t="n">
+        <v>11.72741637441755</v>
+      </c>
+      <c r="O141" t="n">
+        <v>9.246190375335642</v>
+      </c>
+      <c r="P141" t="n">
+        <v>9.444079807917923</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>13.269521268293</v>
+      </c>
+      <c r="R141" t="n">
+        <v>17.48903865183343</v>
+      </c>
+      <c r="S141" t="n">
+        <v>16.35651609476309</v>
+      </c>
+      <c r="T141" t="n">
+        <v>15.65982356526852</v>
+      </c>
+      <c r="U141" t="n">
+        <v>14.58983879407908</v>
+      </c>
+      <c r="V141" t="n">
+        <v>15.66165215649879</v>
+      </c>
+      <c r="W141" t="n">
+        <v>15.66274960413754</v>
+      </c>
+      <c r="X141" t="n">
+        <v>16.34842384867159</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>15.52049313811071</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>14.08738503310578</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>15.08051423124714</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>16.08066302611237</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>14.28499781471052</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>12.00596134376102</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>22.49046145681823</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>16.98013040166097</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>13.93144855218142</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>13.86697273144796</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>13.06860813541699</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>15.42020480907227</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>22.17715823463816</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>20.12766331467909</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>20.5154336349905</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>22.18703740977006</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>-0.09241467722216978</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.01926554087520937</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.08148030426851527</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026 - 05</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Milho</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>43.4194880683358</v>
+      </c>
+      <c r="D142" t="n">
+        <v>38.90070596838311</v>
+      </c>
+      <c r="E142" t="n">
+        <v>42.52354496292463</v>
+      </c>
+      <c r="F142" t="n">
+        <v>50.76767745504062</v>
+      </c>
+      <c r="G142" t="n">
+        <v>51.97422924772828</v>
+      </c>
+      <c r="H142" t="n">
+        <v>44.8761667759638</v>
+      </c>
+      <c r="I142" t="n">
+        <v>42.0821823101972</v>
+      </c>
+      <c r="J142" t="n">
+        <v>39.68902879383995</v>
+      </c>
+      <c r="K142" t="n">
+        <v>35.43314466176248</v>
+      </c>
+      <c r="L142" t="n">
+        <v>35.13763885478109</v>
+      </c>
+      <c r="M142" t="n">
+        <v>40.77317891526427</v>
+      </c>
+      <c r="N142" t="n">
+        <v>42.62084701481389</v>
+      </c>
+      <c r="O142" t="n">
+        <v>40.40190106833456</v>
+      </c>
+      <c r="P142" t="n">
+        <v>48.9356858244733</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>65.05494284864824</v>
+      </c>
+      <c r="R142" t="n">
+        <v>49.1171118790292</v>
+      </c>
+      <c r="S142" t="n">
+        <v>37.12467395475002</v>
+      </c>
+      <c r="T142" t="n">
+        <v>40.36781688146018</v>
+      </c>
+      <c r="U142" t="n">
+        <v>59.73702779135643</v>
+      </c>
+      <c r="V142" t="n">
+        <v>71.9424976443164</v>
+      </c>
+      <c r="W142" t="n">
+        <v>48.66101223876702</v>
+      </c>
+      <c r="X142" t="n">
+        <v>47.53048538240477</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>63.41132511688639</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>78.4716343896059</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>82.2896070920297</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>78.01489012789531</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>81.92578117456998</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>77.90139823617405</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>89.44220602390878</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>81.86968725208199</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>103.2912422814695</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>130.3596397485167</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>141.6236934780882</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>158.9863650527674</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>156.9732957010609</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>129.7348528217692</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>172.478512589381</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>162.2125470409914</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>-0.1735227814236917</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.3294693664649497</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>-0.05952025788180193</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026 - 05</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Pimenta-do-reino</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>1.380059304783311</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.8876307218887364</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.71043330302719</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.276852404640777</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.4071658434192372</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.5350997117099532</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.5461375582648994</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.4568165356557429</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.6197307228413752</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.8181146157444662</v>
+      </c>
+      <c r="M143" t="n">
+        <v>1.200159915448638</v>
+      </c>
+      <c r="N143" t="n">
+        <v>1.677522898596535</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.8808386595608525</v>
+      </c>
+      <c r="P143" t="n">
+        <v>1.003129443629904</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>1.050956054685326</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.7682999777924379</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.8051500994087953</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.7619052792046166</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.9090523581807116</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.8770047141070562</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.7582985194677337</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.7929601610476644</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.976829492000535</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>1.096301754944326</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>1.104856458395606</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>1.51430924895346</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>2.631257477882794</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>2.528378634412434</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>2.530176771282609</v>
+      </c>
+      <c r="AF143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AN143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AP143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AQ143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AR143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026 - 05</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Soja</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>63.79383203308003</v>
+      </c>
+      <c r="D144" t="n">
+        <v>40.73751008328788</v>
+      </c>
+      <c r="E144" t="n">
+        <v>37.3979567538245</v>
+      </c>
+      <c r="F144" t="n">
+        <v>51.06198793311498</v>
+      </c>
+      <c r="G144" t="n">
+        <v>58.90984743076982</v>
+      </c>
+      <c r="H144" t="n">
+        <v>52.3449231585727</v>
+      </c>
+      <c r="I144" t="n">
+        <v>42.82474472746183</v>
+      </c>
+      <c r="J144" t="n">
+        <v>49.82772105488453</v>
+      </c>
+      <c r="K144" t="n">
+        <v>60.92947566874753</v>
+      </c>
+      <c r="L144" t="n">
+        <v>58.33618423117571</v>
+      </c>
+      <c r="M144" t="n">
+        <v>60.70572869853149</v>
+      </c>
+      <c r="N144" t="n">
+        <v>61.34307576287534</v>
+      </c>
+      <c r="O144" t="n">
+        <v>79.54582796166281</v>
+      </c>
+      <c r="P144" t="n">
+        <v>110.2682242750697</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>136.1023686348538</v>
+      </c>
+      <c r="R144" t="n">
+        <v>127.2317596556561</v>
+      </c>
+      <c r="S144" t="n">
+        <v>90.86753914012117</v>
+      </c>
+      <c r="T144" t="n">
+        <v>79.42990071475087</v>
+      </c>
+      <c r="U144" t="n">
+        <v>100.7242825981329</v>
+      </c>
+      <c r="V144" t="n">
+        <v>131.4735684013729</v>
+      </c>
+      <c r="W144" t="n">
+        <v>127.5540286810952</v>
+      </c>
+      <c r="X144" t="n">
+        <v>124.9610243776273</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>139.4738817866509</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>162.9333147057726</v>
+      </c>
+      <c r="AA144" t="n">
+        <v>192.8641520771839</v>
+      </c>
+      <c r="AB144" t="n">
+        <v>195.2990303257389</v>
+      </c>
+      <c r="AC144" t="n">
+        <v>214.7299974725507</v>
+      </c>
+      <c r="AD144" t="n">
+        <v>216.1087678810975</v>
+      </c>
+      <c r="AE144" t="n">
+        <v>220.6788659239642</v>
+      </c>
+      <c r="AF144" t="n">
+        <v>247.3524855945354</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>223.5933647967575</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>319.4006022407326</v>
+      </c>
+      <c r="AI144" t="n">
+        <v>407.4756900088381</v>
+      </c>
+      <c r="AJ144" t="n">
+        <v>358.4263661571826</v>
+      </c>
+      <c r="AK144" t="n">
+        <v>366.9599033097784</v>
+      </c>
+      <c r="AL144" t="n">
+        <v>308.6268851988032</v>
+      </c>
+      <c r="AM144" t="n">
+        <v>341.6700101532501</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>338.5046011647456</v>
+      </c>
+      <c r="AO144" t="n">
+        <v>-0.1589629209754069</v>
+      </c>
+      <c r="AP144" t="n">
+        <v>0.1070649594676825</v>
+      </c>
+      <c r="AQ144" t="n">
+        <v>-0.00926452101278874</v>
+      </c>
+      <c r="AR144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026 - 05</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>8.77179943579495</v>
+      </c>
+      <c r="D145" t="n">
+        <v>10.81954499441043</v>
+      </c>
+      <c r="E145" t="n">
+        <v>8.745445478149685</v>
+      </c>
+      <c r="F145" t="n">
+        <v>6.794400043021859</v>
+      </c>
+      <c r="G145" t="n">
+        <v>7.408589041360419</v>
+      </c>
+      <c r="H145" t="n">
+        <v>12.31168971871504</v>
+      </c>
+      <c r="I145" t="n">
+        <v>10.73454558140011</v>
+      </c>
+      <c r="J145" t="n">
+        <v>8.483595147250693</v>
+      </c>
+      <c r="K145" t="n">
+        <v>7.463309205390681</v>
+      </c>
+      <c r="L145" t="n">
+        <v>9.414761520875384</v>
+      </c>
+      <c r="M145" t="n">
+        <v>9.486714043079763</v>
+      </c>
+      <c r="N145" t="n">
+        <v>8.612372434499731</v>
+      </c>
+      <c r="O145" t="n">
+        <v>7.921897429811678</v>
+      </c>
+      <c r="P145" t="n">
+        <v>9.597777367291295</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>11.40338842259808</v>
+      </c>
+      <c r="R145" t="n">
+        <v>12.4990476558596</v>
+      </c>
+      <c r="S145" t="n">
+        <v>11.83861216752388</v>
+      </c>
+      <c r="T145" t="n">
+        <v>10.26272770289347</v>
+      </c>
+      <c r="U145" t="n">
+        <v>11.46632594347934</v>
+      </c>
+      <c r="V145" t="n">
+        <v>12.7130298561733</v>
+      </c>
+      <c r="W145" t="n">
+        <v>15.08371728678626</v>
+      </c>
+      <c r="X145" t="n">
+        <v>15.00651985031622</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>16.47712322365001</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>15.44168675478152</v>
+      </c>
+      <c r="AA145" t="n">
+        <v>29.40142762115302</v>
+      </c>
+      <c r="AB145" t="n">
+        <v>30.88187296762776</v>
+      </c>
+      <c r="AC145" t="n">
+        <v>28.63328721687014</v>
+      </c>
+      <c r="AD145" t="n">
+        <v>16.32382108605849</v>
+      </c>
+      <c r="AE145" t="n">
+        <v>15.42101018546261</v>
+      </c>
+      <c r="AF145" t="n">
+        <v>16.29336253043553</v>
+      </c>
+      <c r="AG145" t="n">
+        <v>16.81668277243556</v>
+      </c>
+      <c r="AH145" t="n">
+        <v>14.60703626380199</v>
+      </c>
+      <c r="AI145" t="n">
+        <v>12.88243616710812</v>
+      </c>
+      <c r="AJ145" t="n">
+        <v>15.86929791573174</v>
+      </c>
+      <c r="AK145" t="n">
+        <v>19.55025315443977</v>
+      </c>
+      <c r="AL145" t="n">
+        <v>21.21743000322762</v>
+      </c>
+      <c r="AM145" t="n">
+        <v>21.30063153482154</v>
+      </c>
+      <c r="AN145" t="n">
+        <v>22.48558340952562</v>
+      </c>
+      <c r="AO145" t="n">
+        <v>0.08527648392160292</v>
+      </c>
+      <c r="AP145" t="n">
+        <v>0.003921376508901675</v>
+      </c>
+      <c r="AQ145" t="n">
+        <v>0.05562989401356311</v>
+      </c>
+      <c r="AR145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026 - 05</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Trigo</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>11.55763020497692</v>
+      </c>
+      <c r="D146" t="n">
+        <v>5.125612249372273</v>
+      </c>
+      <c r="E146" t="n">
+        <v>4.625188178500744</v>
+      </c>
+      <c r="F146" t="n">
+        <v>5.552795635322345</v>
+      </c>
+      <c r="G146" t="n">
+        <v>3.645049121047442</v>
+      </c>
+      <c r="H146" t="n">
+        <v>3.097659007419708</v>
+      </c>
+      <c r="I146" t="n">
+        <v>2.241254618063041</v>
+      </c>
+      <c r="J146" t="n">
+        <v>5.782917128216589</v>
+      </c>
+      <c r="K146" t="n">
+        <v>3.212169221939359</v>
+      </c>
+      <c r="L146" t="n">
+        <v>2.882312762932293</v>
+      </c>
+      <c r="M146" t="n">
+        <v>3.601894930117003</v>
+      </c>
+      <c r="N146" t="n">
+        <v>2.445027344625021</v>
+      </c>
+      <c r="O146" t="n">
+        <v>5.003385661699298</v>
+      </c>
+      <c r="P146" t="n">
+        <v>6.038851738049833</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>11.90196891895424</v>
+      </c>
+      <c r="R146" t="n">
+        <v>9.270030665996504</v>
+      </c>
+      <c r="S146" t="n">
+        <v>5.907938764858028</v>
+      </c>
+      <c r="T146" t="n">
+        <v>3.045417064604713</v>
+      </c>
+      <c r="U146" t="n">
+        <v>6.233125373000965</v>
+      </c>
+      <c r="V146" t="n">
+        <v>9.464172255021596</v>
+      </c>
+      <c r="W146" t="n">
+        <v>6.54792126957445</v>
+      </c>
+      <c r="X146" t="n">
+        <v>7.334622120841716</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>6.319421667936391</v>
+      </c>
+      <c r="Z146" t="n">
+        <v>7.574603602849498</v>
+      </c>
+      <c r="AA146" t="n">
+        <v>10.10446003152486</v>
+      </c>
+      <c r="AB146" t="n">
+        <v>8.637679656511066</v>
+      </c>
+      <c r="AC146" t="n">
+        <v>7.115158237116658</v>
+      </c>
+      <c r="AD146" t="n">
+        <v>9.314530740044514</v>
+      </c>
+      <c r="AE146" t="n">
+        <v>4.733582872501731</v>
+      </c>
+      <c r="AF146" t="n">
+        <v>7.625583375193383</v>
+      </c>
+      <c r="AG146" t="n">
+        <v>7.290574217714846</v>
+      </c>
+      <c r="AH146" t="n">
+        <v>10.5895019165204</v>
+      </c>
+      <c r="AI146" t="n">
+        <v>13.90858414856488</v>
+      </c>
+      <c r="AJ146" t="n">
+        <v>19.57430349463462</v>
+      </c>
+      <c r="AK146" t="n">
+        <v>11.414256557668</v>
+      </c>
+      <c r="AL146" t="n">
+        <v>10.88521749610368</v>
+      </c>
+      <c r="AM146" t="n">
+        <v>10.8004407292026</v>
+      </c>
+      <c r="AN146" t="n">
+        <v>8.833777335580555</v>
+      </c>
+      <c r="AO146" t="n">
+        <v>-0.04634897234799917</v>
+      </c>
+      <c r="AP146" t="n">
+        <v>-0.007788247403547</v>
+      </c>
+      <c r="AQ146" t="n">
+        <v>-0.1820910315543435</v>
+      </c>
+      <c r="AR146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026 - 05</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Uva</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>2.460982234399658</v>
+      </c>
+      <c r="D147" t="n">
+        <v>2.829591922871551</v>
+      </c>
+      <c r="E147" t="n">
+        <v>1.233522523568862</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0.2731968448162353</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0.3866281445312363</v>
+      </c>
+      <c r="H147" t="n">
+        <v>1.420414123672897</v>
+      </c>
+      <c r="I147" t="n">
+        <v>2.430297541433831</v>
+      </c>
+      <c r="J147" t="n">
+        <v>1.0438869119899</v>
+      </c>
+      <c r="K147" t="n">
+        <v>1.749744821233621</v>
+      </c>
+      <c r="L147" t="n">
+        <v>5.611182846321933</v>
+      </c>
+      <c r="M147" t="n">
+        <v>4.642963810796914</v>
+      </c>
+      <c r="N147" t="n">
+        <v>1.831049550977555</v>
+      </c>
+      <c r="O147" t="n">
+        <v>3.788327816475808</v>
+      </c>
+      <c r="P147" t="n">
+        <v>3.577611668251761</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>4.666113230411304</v>
+      </c>
+      <c r="R147" t="n">
+        <v>8.60556330480337</v>
+      </c>
+      <c r="S147" t="n">
+        <v>3.502734189584765</v>
+      </c>
+      <c r="T147" t="n">
+        <v>3.062421953688789</v>
+      </c>
+      <c r="U147" t="n">
+        <v>6.806481003937975</v>
+      </c>
+      <c r="V147" t="n">
+        <v>3.360813438041905</v>
+      </c>
+      <c r="W147" t="n">
+        <v>10.72734940200247</v>
+      </c>
+      <c r="X147" t="n">
+        <v>8.602727370409033</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>11.68942685405787</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>9.81112623219369</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>8.576031451780871</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>8.889560047303076</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>7.415920832045225</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>6.461572576348968</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>10.65515689359201</v>
+      </c>
+      <c r="AF147" t="n">
+        <v>9.070815343401341</v>
+      </c>
+      <c r="AG147" t="n">
+        <v>8.849898333785069</v>
+      </c>
+      <c r="AH147" t="n">
+        <v>7.718741752378033</v>
+      </c>
+      <c r="AI147" t="n">
+        <v>7.561529542757783</v>
+      </c>
+      <c r="AJ147" t="n">
+        <v>6.904272430901575</v>
+      </c>
+      <c r="AK147" t="n">
+        <v>8.365375352452833</v>
+      </c>
+      <c r="AL147" t="n">
+        <v>11.57908217282091</v>
+      </c>
+      <c r="AM147" t="n">
+        <v>13.19173056075106</v>
+      </c>
+      <c r="AN147" t="n">
+        <v>11.69388567922563</v>
+      </c>
+      <c r="AO147" t="n">
+        <v>0.3841676774761547</v>
+      </c>
+      <c r="AP147" t="n">
+        <v>0.1392725575188896</v>
+      </c>
+      <c r="AQ147" t="n">
+        <v>-0.1135442294418839</v>
+      </c>
+      <c r="AR147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026 - 05</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Maçã</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y148" t="n">
+        <v>6.442161855452019</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>6.882322269727479</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>7.486686069264366</v>
+      </c>
+      <c r="AB148" t="n">
+        <v>8.354752442085369</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>7.262840886042798</v>
+      </c>
+      <c r="AD148" t="n">
+        <v>8.1056870607901</v>
+      </c>
+      <c r="AE148" t="n">
+        <v>6.362375385995544</v>
+      </c>
+      <c r="AF148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AN148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AP148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AQ148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AR148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026 - 05</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>TOTAL LAVOURAS</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>304.5059249432</v>
+      </c>
+      <c r="D149" t="n">
+        <v>268.7780991298671</v>
+      </c>
+      <c r="E149" t="n">
+        <v>267.301688015015</v>
+      </c>
+      <c r="F149" t="n">
+        <v>288.4728419507888</v>
+      </c>
+      <c r="G149" t="n">
+        <v>278.5903661746033</v>
+      </c>
+      <c r="H149" t="n">
+        <v>293.4428654262904</v>
+      </c>
+      <c r="I149" t="n">
+        <v>273.3945589159077</v>
+      </c>
+      <c r="J149" t="n">
+        <v>251.5876176879289</v>
+      </c>
+      <c r="K149" t="n">
+        <v>304.22068718141</v>
+      </c>
+      <c r="L149" t="n">
+        <v>316.7084799082954</v>
+      </c>
+      <c r="M149" t="n">
+        <v>316.5930960078463</v>
+      </c>
+      <c r="N149" t="n">
+        <v>292.3276509045822</v>
+      </c>
+      <c r="O149" t="n">
+        <v>324.7219575756753</v>
+      </c>
+      <c r="P149" t="n">
+        <v>387.8915882297557</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>440.2539898399771</v>
+      </c>
+      <c r="R149" t="n">
+        <v>437.0306077511104</v>
+      </c>
+      <c r="S149" t="n">
+        <v>369.489662314714</v>
+      </c>
+      <c r="T149" t="n">
+        <v>371.7468975223431</v>
+      </c>
+      <c r="U149" t="n">
+        <v>419.8203685028828</v>
+      </c>
+      <c r="V149" t="n">
+        <v>482.0574443525242</v>
+      </c>
+      <c r="W149" t="n">
+        <v>457.8907255829254</v>
+      </c>
+      <c r="X149" t="n">
+        <v>474.8832877618106</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>551.5182348472115</v>
+      </c>
+      <c r="Z149" t="n">
+        <v>581.5092335574089</v>
+      </c>
+      <c r="AA149" t="n">
+        <v>632.6857589717706</v>
+      </c>
+      <c r="AB149" t="n">
+        <v>640.8257792480607</v>
+      </c>
+      <c r="AC149" t="n">
+        <v>643.1509339913397</v>
+      </c>
+      <c r="AD149" t="n">
+        <v>651.2837323077031</v>
+      </c>
+      <c r="AE149" t="n">
+        <v>653.9877760617894</v>
+      </c>
+      <c r="AF149" t="n">
+        <v>631.7154954844698</v>
+      </c>
+      <c r="AG149" t="n">
+        <v>622.6310093579981</v>
+      </c>
+      <c r="AH149" t="n">
+        <v>759.0018017768297</v>
+      </c>
+      <c r="AI149" t="n">
+        <v>860.2301054393026</v>
+      </c>
+      <c r="AJ149" t="n">
+        <v>865.093481015625</v>
+      </c>
+      <c r="AK149" t="n">
+        <v>900.2667536762258</v>
+      </c>
+      <c r="AL149" t="n">
+        <v>873.2757950921828</v>
+      </c>
+      <c r="AM149" t="n">
+        <v>966.0791700328857</v>
+      </c>
+      <c r="AN149" t="n">
+        <v>908.8746985300089</v>
+      </c>
+      <c r="AO149" t="n">
+        <v>-0.02998106780443222</v>
+      </c>
+      <c r="AP149" t="n">
+        <v>0.1062704078851822</v>
+      </c>
+      <c r="AQ149" t="n">
+        <v>-0.05921302650685401</v>
+      </c>
+      <c r="AR149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026 - 05</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Bovinos</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>62.30292384906267</v>
+      </c>
+      <c r="O150" t="n">
+        <v>68.87007312760394</v>
+      </c>
+      <c r="P150" t="n">
+        <v>73.08415917461349</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>73.76095285658147</v>
+      </c>
+      <c r="R150" t="n">
+        <v>82.98978006816019</v>
+      </c>
+      <c r="S150" t="n">
+        <v>80.57121215351332</v>
+      </c>
+      <c r="T150" t="n">
+        <v>83.65275485124702</v>
+      </c>
+      <c r="U150" t="n">
+        <v>90.91121409219276</v>
+      </c>
+      <c r="V150" t="n">
+        <v>100.3766735586636</v>
+      </c>
+      <c r="W150" t="n">
+        <v>99.32972661733753</v>
+      </c>
+      <c r="X150" t="n">
+        <v>104.7234308477615</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>110.708987914042</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>112.3591263763817</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>121.7575514502388</v>
+      </c>
+      <c r="AB150" t="n">
+        <v>139.877246616092</v>
+      </c>
+      <c r="AC150" t="n">
+        <v>144.6912832677485</v>
+      </c>
+      <c r="AD150" t="n">
+        <v>135.437860783273</v>
+      </c>
+      <c r="AE150" t="n">
+        <v>132.9088651453625</v>
+      </c>
+      <c r="AF150" t="n">
+        <v>133.7995132039018</v>
+      </c>
+      <c r="AG150" t="n">
+        <v>143.2698691255414</v>
+      </c>
+      <c r="AH150" t="n">
+        <v>164.3394156604741</v>
+      </c>
+      <c r="AI150" t="n">
+        <v>167.582884168905</v>
+      </c>
+      <c r="AJ150" t="n">
+        <v>163.5256644880886</v>
+      </c>
+      <c r="AK150" t="n">
+        <v>156.1187551011002</v>
+      </c>
+      <c r="AL150" t="n">
+        <v>176.6573579144026</v>
+      </c>
+      <c r="AM150" t="n">
+        <v>228.4339159233654</v>
+      </c>
+      <c r="AN150" t="n">
+        <v>248.7454736248581</v>
+      </c>
+      <c r="AO150" t="n">
+        <v>0.1315575620623022</v>
+      </c>
+      <c r="AP150" t="n">
+        <v>0.2930902998903142</v>
+      </c>
+      <c r="AQ150" t="n">
+        <v>0.08891655873161519</v>
+      </c>
+      <c r="AR150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026 - 05</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Suínos</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
+        <v>11.28089694773543</v>
+      </c>
+      <c r="O151" t="n">
+        <v>13.53394684706551</v>
+      </c>
+      <c r="P151" t="n">
+        <v>13.87120729808829</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>14.8246841765255</v>
+      </c>
+      <c r="R151" t="n">
+        <v>16.66759804062853</v>
+      </c>
+      <c r="S151" t="n">
+        <v>19.32460916454682</v>
+      </c>
+      <c r="T151" t="n">
+        <v>16.99877458603344</v>
+      </c>
+      <c r="U151" t="n">
+        <v>18.17694275518034</v>
+      </c>
+      <c r="V151" t="n">
+        <v>21.52335736928301</v>
+      </c>
+      <c r="W151" t="n">
+        <v>21.75682790976247</v>
+      </c>
+      <c r="X151" t="n">
+        <v>23.93469208557863</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>23.97220283149241</v>
+      </c>
+      <c r="Z151" t="n">
+        <v>22.50868623998163</v>
+      </c>
+      <c r="AA151" t="n">
+        <v>26.06165284995253</v>
+      </c>
+      <c r="AB151" t="n">
+        <v>27.37311758573809</v>
+      </c>
+      <c r="AC151" t="n">
+        <v>29.25337710387489</v>
+      </c>
+      <c r="AD151" t="n">
+        <v>26.99661244094401</v>
+      </c>
+      <c r="AE151" t="n">
+        <v>40.24429142748428</v>
+      </c>
+      <c r="AF151" t="n">
+        <v>32.02068028369401</v>
+      </c>
+      <c r="AG151" t="n">
+        <v>39.63982340078829</v>
+      </c>
+      <c r="AH151" t="n">
+        <v>53.29269095221012</v>
+      </c>
+      <c r="AI151" t="n">
+        <v>49.50986538160604</v>
+      </c>
+      <c r="AJ151" t="n">
+        <v>43.19905004878343</v>
+      </c>
+      <c r="AK151" t="n">
+        <v>49.42493037623742</v>
+      </c>
+      <c r="AL151" t="n">
+        <v>57.96739877882249</v>
+      </c>
+      <c r="AM151" t="n">
+        <v>66.44729019724684</v>
+      </c>
+      <c r="AN151" t="n">
+        <v>52.95348306693352</v>
+      </c>
+      <c r="AO151" t="n">
+        <v>0.1728372369481805</v>
+      </c>
+      <c r="AP151" t="n">
+        <v>0.1462872510595101</v>
+      </c>
+      <c r="AQ151" t="n">
+        <v>-0.2030753562749865</v>
+      </c>
+      <c r="AR151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026 - 05</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Frango</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N152" t="n">
+        <v>31.12078274947915</v>
+      </c>
+      <c r="O152" t="n">
+        <v>32.47814229414293</v>
+      </c>
+      <c r="P152" t="n">
+        <v>36.88156271033459</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>41.98645554156638</v>
+      </c>
+      <c r="R152" t="n">
+        <v>44.61141770091304</v>
+      </c>
+      <c r="S152" t="n">
+        <v>52.80086549514002</v>
+      </c>
+      <c r="T152" t="n">
+        <v>48.30575209326803</v>
+      </c>
+      <c r="U152" t="n">
+        <v>65.03763928514846</v>
+      </c>
+      <c r="V152" t="n">
+        <v>73.27727086262797</v>
+      </c>
+      <c r="W152" t="n">
+        <v>70.04530818375859</v>
+      </c>
+      <c r="X152" t="n">
+        <v>68.78628933024267</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>73.98856222935328</v>
+      </c>
+      <c r="Z152" t="n">
+        <v>74.50988354072354</v>
+      </c>
+      <c r="AA152" t="n">
+        <v>82.66323747286255</v>
+      </c>
+      <c r="AB152" t="n">
+        <v>80.12527438072847</v>
+      </c>
+      <c r="AC152" t="n">
+        <v>85.28984059988629</v>
+      </c>
+      <c r="AD152" t="n">
+        <v>87.04854749759816</v>
+      </c>
+      <c r="AE152" t="n">
+        <v>79.17571102467249</v>
+      </c>
+      <c r="AF152" t="n">
+        <v>78.71422129075617</v>
+      </c>
+      <c r="AG152" t="n">
+        <v>91.73067250585986</v>
+      </c>
+      <c r="AH152" t="n">
+        <v>90.47896775964411</v>
+      </c>
+      <c r="AI152" t="n">
+        <v>105.5968491696818</v>
+      </c>
+      <c r="AJ152" t="n">
+        <v>102.9220781552876</v>
+      </c>
+      <c r="AK152" t="n">
+        <v>99.45083321566145</v>
+      </c>
+      <c r="AL152" t="n">
+        <v>110.6826009873284</v>
+      </c>
+      <c r="AM152" t="n">
+        <v>119.0077023293234</v>
+      </c>
+      <c r="AN152" t="n">
+        <v>106.6812544721081</v>
+      </c>
+      <c r="AO152" t="n">
+        <v>0.1129378951236195</v>
+      </c>
+      <c r="AP152" t="n">
+        <v>0.07521598939428675</v>
+      </c>
+      <c r="AQ152" t="n">
+        <v>-0.1035768913772062</v>
+      </c>
+      <c r="AR152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026 - 05</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Leite</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N153" t="n">
+        <v>24.60899483861452</v>
+      </c>
+      <c r="O153" t="n">
+        <v>23.68077500270575</v>
+      </c>
+      <c r="P153" t="n">
+        <v>23.97869480874057</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>26.40572594664108</v>
+      </c>
+      <c r="R153" t="n">
+        <v>26.98793424835438</v>
+      </c>
+      <c r="S153" t="n">
+        <v>30.35378335941961</v>
+      </c>
+      <c r="T153" t="n">
+        <v>28.99307333768375</v>
+      </c>
+      <c r="U153" t="n">
+        <v>35.64264192993066</v>
+      </c>
+      <c r="V153" t="n">
+        <v>40.09596717615509</v>
+      </c>
+      <c r="W153" t="n">
+        <v>40.87827960584094</v>
+      </c>
+      <c r="X153" t="n">
+        <v>45.14431925794133</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>46.53844848194593</v>
+      </c>
+      <c r="Z153" t="n">
+        <v>48.63088050979859</v>
+      </c>
+      <c r="AA153" t="n">
+        <v>56.27554095476584</v>
+      </c>
+      <c r="AB153" t="n">
+        <v>60.7700686252756</v>
+      </c>
+      <c r="AC153" t="n">
+        <v>54.85537502702191</v>
+      </c>
+      <c r="AD153" t="n">
+        <v>50.89950045760099</v>
+      </c>
+      <c r="AE153" t="n">
+        <v>56.71252166075114</v>
+      </c>
+      <c r="AF153" t="n">
+        <v>55.86954010649422</v>
+      </c>
+      <c r="AG153" t="n">
+        <v>55.35178162451729</v>
+      </c>
+      <c r="AH153" t="n">
+        <v>56.90933919924671</v>
+      </c>
+      <c r="AI153" t="n">
+        <v>56.97210980829882</v>
+      </c>
+      <c r="AJ153" t="n">
+        <v>62.20210471813988</v>
+      </c>
+      <c r="AK153" t="n">
+        <v>69.94644514414151</v>
+      </c>
+      <c r="AL153" t="n">
+        <v>70.87846841118701</v>
+      </c>
+      <c r="AM153" t="n">
+        <v>77.3226551840382</v>
+      </c>
+      <c r="AN153" t="n">
+        <v>73.58675470279951</v>
+      </c>
+      <c r="AO153" t="n">
+        <v>0.01332481250655193</v>
+      </c>
+      <c r="AP153" t="n">
+        <v>0.09091882086766523</v>
+      </c>
+      <c r="AQ153" t="n">
+        <v>-0.04831572935961326</v>
+      </c>
+      <c r="AR153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026 - 05</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Ovos</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N154" t="n">
+        <v>9.621964055749116</v>
+      </c>
+      <c r="O154" t="n">
+        <v>9.481655017624155</v>
+      </c>
+      <c r="P154" t="n">
+        <v>9.768747358364314</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>11.81645956024769</v>
+      </c>
+      <c r="R154" t="n">
+        <v>11.97611772870785</v>
+      </c>
+      <c r="S154" t="n">
+        <v>12.05753205056614</v>
+      </c>
+      <c r="T154" t="n">
+        <v>11.45343706152909</v>
+      </c>
+      <c r="U154" t="n">
+        <v>12.17258472706399</v>
+      </c>
+      <c r="V154" t="n">
+        <v>13.1400394841329</v>
+      </c>
+      <c r="W154" t="n">
+        <v>13.10772815226853</v>
+      </c>
+      <c r="X154" t="n">
+        <v>12.74875384897519</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>15.02234789798331</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>17.60987119752638</v>
+      </c>
+      <c r="AA154" t="n">
+        <v>20.71148224905026</v>
+      </c>
+      <c r="AB154" t="n">
+        <v>23.27016259014241</v>
+      </c>
+      <c r="AC154" t="n">
+        <v>23.69307957926366</v>
+      </c>
+      <c r="AD154" t="n">
+        <v>25.54340663431272</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>21.04981963855827</v>
+      </c>
+      <c r="AF154" t="n">
+        <v>19.14806604974631</v>
+      </c>
+      <c r="AG154" t="n">
+        <v>19.38979182984412</v>
+      </c>
+      <c r="AH154" t="n">
+        <v>21.29385247866472</v>
+      </c>
+      <c r="AI154" t="n">
+        <v>19.95453389592644</v>
+      </c>
+      <c r="AJ154" t="n">
+        <v>22.1401872911536</v>
+      </c>
+      <c r="AK154" t="n">
+        <v>27.28145778475978</v>
+      </c>
+      <c r="AL154" t="n">
+        <v>27.75779804243139</v>
+      </c>
+      <c r="AM154" t="n">
+        <v>30.66880424995807</v>
+      </c>
+      <c r="AN154" t="n">
+        <v>28.25986592617908</v>
+      </c>
+      <c r="AO154" t="n">
+        <v>0.01746022010369619</v>
+      </c>
+      <c r="AP154" t="n">
+        <v>0.1048716545554815</v>
+      </c>
+      <c r="AQ154" t="n">
+        <v>-0.07854686162999935</v>
+      </c>
+      <c r="AR154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026 - 05</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>TOTAL PECUÁRIA</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" t="n">
+        <v>138.9355624406409</v>
+      </c>
+      <c r="O155" t="n">
+        <v>148.0445922891423</v>
+      </c>
+      <c r="P155" t="n">
+        <v>157.5843713501413</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>168.7942780815621</v>
+      </c>
+      <c r="R155" t="n">
+        <v>183.232847786764</v>
+      </c>
+      <c r="S155" t="n">
+        <v>195.1080022231859</v>
+      </c>
+      <c r="T155" t="n">
+        <v>189.4037919297613</v>
+      </c>
+      <c r="U155" t="n">
+        <v>221.9410227895162</v>
+      </c>
+      <c r="V155" t="n">
+        <v>248.4133084508626</v>
+      </c>
+      <c r="W155" t="n">
+        <v>245.117870468968</v>
+      </c>
+      <c r="X155" t="n">
+        <v>255.3374853704993</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>270.2305493548169</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>275.6184478644118</v>
+      </c>
+      <c r="AA155" t="n">
+        <v>307.46946497687</v>
+      </c>
+      <c r="AB155" t="n">
+        <v>331.4158697979765</v>
+      </c>
+      <c r="AC155" t="n">
+        <v>337.7829555777953</v>
+      </c>
+      <c r="AD155" t="n">
+        <v>325.9259278137289</v>
+      </c>
+      <c r="AE155" t="n">
+        <v>330.0912088968287</v>
+      </c>
+      <c r="AF155" t="n">
+        <v>319.5520209345925</v>
+      </c>
+      <c r="AG155" t="n">
+        <v>349.381938486551</v>
+      </c>
+      <c r="AH155" t="n">
+        <v>386.3142660502397</v>
+      </c>
+      <c r="AI155" t="n">
+        <v>399.6162424244181</v>
+      </c>
+      <c r="AJ155" t="n">
+        <v>393.9890847014531</v>
+      </c>
+      <c r="AK155" t="n">
+        <v>402.2224216219004</v>
+      </c>
+      <c r="AL155" t="n">
+        <v>443.9436241341718</v>
+      </c>
+      <c r="AM155" t="n">
+        <v>521.8803678839319</v>
+      </c>
+      <c r="AN155" t="n">
+        <v>510.2268317928784</v>
+      </c>
+      <c r="AO155" t="n">
+        <v>0.1037266951554738</v>
+      </c>
+      <c r="AP155" t="n">
+        <v>0.1755554973939788</v>
+      </c>
+      <c r="AQ155" t="n">
+        <v>-0.02232989935663809</v>
+      </c>
+      <c r="AR155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026 - 05</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>VBP TOTAL</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>304.5059249432</v>
+      </c>
+      <c r="D156" t="n">
+        <v>268.7780991298671</v>
+      </c>
+      <c r="E156" t="n">
+        <v>267.301688015015</v>
+      </c>
+      <c r="F156" t="n">
+        <v>288.4728419507888</v>
+      </c>
+      <c r="G156" t="n">
+        <v>278.5903661746033</v>
+      </c>
+      <c r="H156" t="n">
+        <v>293.4428654262904</v>
+      </c>
+      <c r="I156" t="n">
+        <v>273.3945589159077</v>
+      </c>
+      <c r="J156" t="n">
+        <v>251.5876176879289</v>
+      </c>
+      <c r="K156" t="n">
+        <v>304.22068718141</v>
+      </c>
+      <c r="L156" t="n">
+        <v>316.7084799082954</v>
+      </c>
+      <c r="M156" t="n">
+        <v>316.5930960078463</v>
+      </c>
+      <c r="N156" t="n">
+        <v>431.2632133452231</v>
+      </c>
+      <c r="O156" t="n">
+        <v>472.7665498648176</v>
+      </c>
+      <c r="P156" t="n">
+        <v>545.475959579897</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>609.0482679215391</v>
+      </c>
+      <c r="R156" t="n">
+        <v>620.2634555378744</v>
+      </c>
+      <c r="S156" t="n">
+        <v>564.5976645379</v>
+      </c>
+      <c r="T156" t="n">
+        <v>561.1506894521044</v>
+      </c>
+      <c r="U156" t="n">
+        <v>641.761391292399</v>
+      </c>
+      <c r="V156" t="n">
+        <v>730.4707528033867</v>
+      </c>
+      <c r="W156" t="n">
+        <v>703.0085960518934</v>
+      </c>
+      <c r="X156" t="n">
+        <v>730.2207731323099</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>821.7487842020284</v>
+      </c>
+      <c r="Z156" t="n">
+        <v>857.1276814218207</v>
+      </c>
+      <c r="AA156" t="n">
+        <v>940.1552239486406</v>
+      </c>
+      <c r="AB156" t="n">
+        <v>972.2416490460373</v>
+      </c>
+      <c r="AC156" t="n">
+        <v>980.933889569135</v>
+      </c>
+      <c r="AD156" t="n">
+        <v>977.209660121432</v>
+      </c>
+      <c r="AE156" t="n">
+        <v>984.0789849586181</v>
+      </c>
+      <c r="AF156" t="n">
+        <v>951.2675164190623</v>
+      </c>
+      <c r="AG156" t="n">
+        <v>972.0129478445491</v>
+      </c>
+      <c r="AH156" t="n">
+        <v>1145.316067827069</v>
+      </c>
+      <c r="AI156" t="n">
+        <v>1259.846347863721</v>
+      </c>
+      <c r="AJ156" t="n">
+        <v>1259.082565717078</v>
+      </c>
+      <c r="AK156" t="n">
+        <v>1302.489175298126</v>
+      </c>
+      <c r="AL156" t="n">
+        <v>1317.219419226355</v>
+      </c>
+      <c r="AM156" t="n">
+        <v>1487.959537916818</v>
+      </c>
+      <c r="AN156" t="n">
+        <v>1419.101530322887</v>
+      </c>
+      <c r="AO156" t="n">
+        <v>0.01130930237854511</v>
+      </c>
+      <c r="AP156" t="n">
+        <v>0.1296216227898799</v>
+      </c>
+      <c r="AQ156" t="n">
+        <v>-0.04627680110867349</v>
+      </c>
+      <c r="AR156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026 - 05</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>0</v>
+      </c>
+      <c r="C157" t="n">
+        <v>0</v>
+      </c>
+      <c r="D157" t="n">
+        <v>0</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0</v>
+      </c>
+      <c r="I157" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" t="n">
+        <v>0</v>
+      </c>
+      <c r="L157" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" t="n">
+        <v>0</v>
+      </c>
+      <c r="N157" t="n">
+        <v>0</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="P157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>0</v>
+      </c>
+      <c r="R157" t="n">
+        <v>0</v>
+      </c>
+      <c r="S157" t="n">
+        <v>0</v>
+      </c>
+      <c r="T157" t="n">
+        <v>0</v>
+      </c>
+      <c r="U157" t="n">
+        <v>0</v>
+      </c>
+      <c r="V157" t="n">
+        <v>0</v>
+      </c>
+      <c r="W157" t="n">
+        <v>0</v>
+      </c>
+      <c r="X157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR157" t="inlineStr">
         <is>
           <t>RO</t>
         </is>
       </c>
-      <c r="AS126" t="inlineStr">
+      <c r="AS157" t="inlineStr">
         <is>
           <t>ALGODÃO</t>
         </is>
       </c>
-      <c r="AT126" t="n">
+      <c r="AT157" t="n">
         <v>2018</v>
       </c>
-      <c r="AU126" t="n">
-        <v>91430521.9375</v>
-      </c>
-      <c r="AV126" t="n">
-        <v>91.43049999999999</v>
-      </c>
-      <c r="AW126" t="inlineStr">
+      <c r="AU157" t="n">
+        <v>92227272.73720001</v>
+      </c>
+      <c r="AV157" t="n">
+        <v>92.2273</v>
+      </c>
+      <c r="AW157" t="inlineStr">
         <is>
           <t>LAVOURAS</t>
         </is>
       </c>
-      <c r="AX126" t="inlineStr">
+      <c r="AX157" t="inlineStr">
         <is>
           <t>RONDÔNIA</t>
         </is>
       </c>
-      <c r="AY126" t="inlineStr">
+      <c r="AY157" t="inlineStr">
         <is>
           <t>NORTE</t>
         </is>
